--- a/data/trans_orig/P34A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34A-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2007</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2007 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>18794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>35509</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63013</t>
+          <t>61910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24652</t>
+          <t>24168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48126</t>
+          <t>46715</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65479</t>
+          <t>66463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101407</t>
+          <t>101780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>425082</t>
+          <t>425200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>489969</t>
+          <t>487448</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>547114</t>
+          <t>545274</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>617997</t>
+          <t>616820</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>990878</t>
+          <t>987609</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1084519</t>
+          <t>1090143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,23%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>473457</t>
+          <t>472880</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>534661</t>
+          <t>536400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>635503</t>
+          <t>638055</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>707950</t>
+          <t>710051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1130134</t>
+          <t>1129073</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1222320</t>
+          <t>1227420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73234</t>
+          <t>72354</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110535</t>
+          <t>109803</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47604</t>
+          <t>47830</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>104295</t>
+          <t>103634</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>150430</t>
+          <t>146376</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>215405</t>
+          <t>213884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>274865</t>
+          <t>273024</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91412</t>
+          <t>92961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131729</t>
+          <t>134852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>315437</t>
+          <t>321849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>388846</t>
+          <t>391362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621684</t>
+          <t>622352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>701111</t>
+          <t>701424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>691907</t>
+          <t>695351</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770785</t>
+          <t>772530</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1343912</t>
+          <t>1342010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1460873</t>
+          <t>1455654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>634746</t>
+          <t>636031</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>719988</t>
+          <t>717090</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>637248</t>
+          <t>642124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>719453</t>
+          <t>719467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1295256</t>
+          <t>1298427</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1410719</t>
+          <t>1410523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36758</t>
+          <t>37201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65953</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25854</t>
+          <t>25914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50736</t>
+          <t>51616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84127</t>
+          <t>83684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88479</t>
+          <t>88175</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126750</t>
+          <t>125989</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61368</t>
+          <t>59508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>132454</t>
+          <t>131956</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178593</t>
+          <t>175295</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>218068</t>
+          <t>218309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>266823</t>
+          <t>265373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>202044</t>
+          <t>203162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>245756</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>433059</t>
+          <t>433305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>496704</t>
+          <t>497464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126193</t>
+          <t>128540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168937</t>
+          <t>173276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158186</t>
+          <t>158789</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202626</t>
+          <t>199821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296421</t>
+          <t>296905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359776</t>
+          <t>359422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124187</t>
+          <t>125444</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172520</t>
+          <t>171384</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42830</t>
+          <t>40857</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71583</t>
+          <t>71785</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>176647</t>
+          <t>176021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>231534</t>
+          <t>231578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>364042</t>
+          <t>362478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>438477</t>
+          <t>439353</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>165692</t>
+          <t>166127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>220333</t>
+          <t>216311</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>543486</t>
+          <t>543886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>636883</t>
+          <t>635218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1299941</t>
+          <t>1304939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1412628</t>
+          <t>1416437</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1477301</t>
+          <t>1481928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1603336</t>
+          <t>1601755</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2817384</t>
+          <t>2813236</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2979872</t>
+          <t>2974585</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1277681</t>
+          <t>1269057</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1387470</t>
+          <t>1384498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1471330</t>
+          <t>1475908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1592159</t>
+          <t>1591174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2777688</t>
+          <t>2775725</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2943935</t>
+          <t>2940722</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2012</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15918</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36121</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24825</t>
+          <t>25391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49689</t>
+          <t>50529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40759</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67661</t>
+          <t>68503</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,49 +3368,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>42574</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29767</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55988</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>4,19%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>42574</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>30913</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>57152</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>92</t>
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78188</t>
+          <t>78332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117332</t>
+          <t>116297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>613615</t>
+          <t>615854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>673527</t>
+          <t>676055</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>760442</t>
+          <t>755049</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>834288</t>
+          <t>830818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1399111</t>
+          <t>1394042</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1488247</t>
+          <t>1490344</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,5%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>225108</t>
+          <t>223727</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>277762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>446170</t>
+          <t>450354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>522760</t>
+          <t>523911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>694340</t>
+          <t>689702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>777762</t>
+          <t>784902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>179142</t>
+          <t>181288</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>234766</t>
+          <t>236941</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>24981</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50010</t>
+          <t>49575</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>210917</t>
+          <t>209781</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>274861</t>
+          <t>273346</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>367576</t>
+          <t>369510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>437704</t>
+          <t>441973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>106995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151581</t>
+          <t>152617</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>491421</t>
+          <t>491024</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>578738</t>
+          <t>578153</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>859890</t>
+          <t>857227</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>952131</t>
+          <t>949367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1025509</t>
+          <t>1019277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1104963</t>
+          <t>1105477</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1896443</t>
+          <t>1897044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2027172</t>
+          <t>2029795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>411651</t>
+          <t>410198</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>489726</t>
+          <t>489969</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>493384</t>
+          <t>493071</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>570929</t>
+          <t>571957</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>927153</t>
+          <t>923247</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1038157</t>
+          <t>1033916</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43431</t>
+          <t>42618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70727</t>
+          <t>71389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34579</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60960</t>
+          <t>61266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98076</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121710</t>
+          <t>120235</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>162258</t>
+          <t>161626</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45619</t>
+          <t>46038</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76915</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>177020</t>
+          <t>176574</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>232173</t>
+          <t>231165</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>195437</t>
+          <t>193637</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241869</t>
+          <t>241179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>270153</t>
+          <t>270505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>313164</t>
+          <t>313887</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>475947</t>
+          <t>478102</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>543580</t>
+          <t>545016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51479</t>
+          <t>50836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83644</t>
+          <t>82627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67353</t>
+          <t>67113</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101741</t>
+          <t>101668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125761</t>
+          <t>126848</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171791</t>
+          <t>174284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>254016</t>
+          <t>254113</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>324440</t>
+          <t>321401</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55171</t>
+          <t>53211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89819</t>
+          <t>89101</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>323420</t>
+          <t>322147</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>395266</t>
+          <t>398225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>553367</t>
+          <t>551385</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>643236</t>
+          <t>647065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204045</t>
+          <t>205093</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266595</t>
+          <t>265099</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>771639</t>
+          <t>778225</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>888485</t>
+          <t>886536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1707181</t>
+          <t>1706904</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1826597</t>
+          <t>1825072</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2089529</t>
+          <t>2092002</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2211797</t>
+          <t>2209766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3829894</t>
+          <t>3834415</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4009205</t>
+          <t>4001015</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>716600</t>
+          <t>721725</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>819659</t>
+          <t>821006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1040181</t>
+          <t>1042616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1159173</t>
+          <t>1154525</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1786660</t>
+          <t>1793730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1937543</t>
+          <t>1944759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2016</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26588</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14515</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33887</t>
+          <t>35028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44451</t>
+          <t>43126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73339</t>
+          <t>72748</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48357</t>
+          <t>49329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72717</t>
+          <t>73189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110296</t>
+          <t>111025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>296571</t>
+          <t>299690</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>351113</t>
+          <t>353863</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>362371</t>
+          <t>363003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>427403</t>
+          <t>428735</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>677060</t>
+          <t>678188</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>760420</t>
+          <t>755920</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>327570</t>
+          <t>328363</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>382879</t>
+          <t>381874</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>527476</t>
+          <t>528798</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>593572</t>
+          <t>593866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>871467</t>
+          <t>878087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>957900</t>
+          <t>958231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141013</t>
+          <t>141490</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>191384</t>
+          <t>191385</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36469</t>
+          <t>35978</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63895</t>
+          <t>64209</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>185788</t>
+          <t>186477</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>244448</t>
+          <t>245483</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>345319</t>
+          <t>348697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>417817</t>
+          <t>419532</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>183279</t>
+          <t>184078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>239895</t>
+          <t>241315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>548454</t>
+          <t>551668</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>636944</t>
+          <t>639833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>814922</t>
+          <t>817009</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>907513</t>
+          <t>911890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>893723</t>
+          <t>889971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>982264</t>
+          <t>983723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1732989</t>
+          <t>1736866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1866218</t>
+          <t>1863251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>620776</t>
+          <t>618059</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>709492</t>
+          <t>708822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>751145</t>
+          <t>746579</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>837587</t>
+          <t>835102</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1393708</t>
+          <t>1395403</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1520251</t>
+          <t>1515975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44971</t>
+          <t>46021</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75354</t>
+          <t>75794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>13440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31872</t>
+          <t>32193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63837</t>
+          <t>64533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99522</t>
+          <t>98880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123042</t>
+          <t>122639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>165299</t>
+          <t>165263</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>79767</t>
+          <t>78021</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116372</t>
+          <t>113393</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212953</t>
+          <t>214876</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>269719</t>
+          <t>273162</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>193791</t>
+          <t>194494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>240700</t>
+          <t>242481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>250272</t>
+          <t>252269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>299897</t>
+          <t>298288</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>458545</t>
+          <t>454131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>527504</t>
+          <t>525334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106558</t>
+          <t>105643</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146048</t>
+          <t>147545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135158</t>
+          <t>136504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>180909</t>
+          <t>177786</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250615</t>
+          <t>254448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>313715</t>
+          <t>312730</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210140</t>
+          <t>211171</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>270729</t>
+          <t>272505</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58804</t>
+          <t>58751</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92536</t>
+          <t>93138</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>281446</t>
+          <t>284681</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>353148</t>
+          <t>356260</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>544329</t>
+          <t>540751</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>634601</t>
+          <t>633183</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>308129</t>
+          <t>307402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>382928</t>
+          <t>378998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>867970</t>
+          <t>865175</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>979780</t>
+          <t>979635</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1352066</t>
+          <t>1350473</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1468966</t>
+          <t>1471597</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1547749</t>
+          <t>1547274</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1672925</t>
+          <t>1669519</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2936690</t>
+          <t>2933607</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3111108</t>
+          <t>3093897</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1091393</t>
+          <t>1089899</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1198720</t>
+          <t>1200840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1441704</t>
+          <t>1445027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1569618</t>
+          <t>1565189</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2570205</t>
+          <t>2570666</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2727966</t>
+          <t>2729724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2023</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22766</t>
+          <t>22987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43435</t>
+          <t>44099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>30908</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>18579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>24453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44231</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>192793</t>
+          <t>194116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>233134</t>
+          <t>234244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>241970</t>
+          <t>242186</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>281717</t>
+          <t>282392</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>451753</t>
+          <t>449593</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>507874</t>
+          <t>505303</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>243316</t>
+          <t>242348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>284892</t>
+          <t>283405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>436058</t>
+          <t>434511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>475885</t>
+          <t>476273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>687830</t>
+          <t>686643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>744130</t>
+          <t>746146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>185742</t>
+          <t>189868</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>319415</t>
+          <t>323994</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96010</t>
+          <t>92890</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>157421</t>
+          <t>158561</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>323677</t>
+          <t>319871</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>468666</t>
+          <t>467022</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>190543</t>
+          <t>195912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>346334</t>
+          <t>343592</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88013</t>
+          <t>83944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150632</t>
+          <t>145634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>337199</t>
+          <t>332184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>479899</t>
+          <t>475526</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>920213</t>
+          <t>918299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1462893</t>
+          <t>1462241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1089331</t>
+          <t>1090279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1488397</t>
+          <t>1501318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2055153</t>
+          <t>2045999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2729122</t>
+          <t>2741059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>428924</t>
+          <t>453954</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>740283</t>
+          <t>744729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>550071</t>
+          <t>561571</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>865965</t>
+          <t>866077</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1145335</t>
+          <t>1126116</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1567990</t>
+          <t>1592285</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97365</t>
+          <t>98802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140657</t>
+          <t>140848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74129</t>
+          <t>73818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105734</t>
+          <t>103880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177380</t>
+          <t>178252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232943</t>
+          <t>233604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83879</t>
+          <t>85325</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>128030</t>
+          <t>126920</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69175</t>
+          <t>67947</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103183</t>
+          <t>101456</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>162596</t>
+          <t>163686</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>217754</t>
+          <t>214221</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>247532</t>
+          <t>242996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>301916</t>
+          <t>299354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>291377</t>
+          <t>290497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>337054</t>
+          <t>337118</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>555538</t>
+          <t>554278</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>622897</t>
+          <t>625917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130142</t>
+          <t>128283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174601</t>
+          <t>175882</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154468</t>
+          <t>155106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193801</t>
+          <t>194929</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>292354</t>
+          <t>295167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353549</t>
+          <t>356072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>313705</t>
+          <t>310490</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>459631</t>
+          <t>457938</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194518</t>
+          <t>193540</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>274294</t>
+          <t>272549</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>548991</t>
+          <t>547303</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>712724</t>
+          <t>712621</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>315806</t>
+          <t>328541</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>473915</t>
+          <t>473320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174673</t>
+          <t>179392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250650</t>
+          <t>251548</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>543536</t>
+          <t>539644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>706003</t>
+          <t>704728</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1402165</t>
+          <t>1402939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2041600</t>
+          <t>2020579</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1661462</t>
+          <t>1656519</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2122719</t>
+          <t>2124193</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3108346</t>
+          <t>3113867</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3885098</t>
+          <t>3932013</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>781516</t>
+          <t>823313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1162127</t>
+          <t>1170032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1165871</t>
+          <t>1163248</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1500338</t>
+          <t>1509427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2095982</t>
+          <t>2087516</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2616851</t>
+          <t>2627564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P34A-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35509</t>
+          <t>36071</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61910</t>
+          <t>62272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24168</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46715</t>
+          <t>47745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66463</t>
+          <t>67607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101780</t>
+          <t>102937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>425200</t>
+          <t>423967</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>487448</t>
+          <t>486299</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>545274</t>
+          <t>546366</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>616820</t>
+          <t>615523</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>987609</t>
+          <t>991388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1090143</t>
+          <t>1084513</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>472880</t>
+          <t>473110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>536400</t>
+          <t>535252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>638055</t>
+          <t>640641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>710051</t>
+          <t>711258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1129073</t>
+          <t>1131113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1227420</t>
+          <t>1222782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72354</t>
+          <t>74133</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>109803</t>
+          <t>111404</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24868</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47830</t>
+          <t>47895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103634</t>
+          <t>104851</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>146376</t>
+          <t>148846</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>213884</t>
+          <t>215496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>273024</t>
+          <t>270890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92961</t>
+          <t>92779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134852</t>
+          <t>133012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>321849</t>
+          <t>316000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>391362</t>
+          <t>388377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622352</t>
+          <t>621887</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>701424</t>
+          <t>702662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>695351</t>
+          <t>693835</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>772530</t>
+          <t>777641</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1342010</t>
+          <t>1339798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1455654</t>
+          <t>1452179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>636031</t>
+          <t>635254</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>717090</t>
+          <t>716991</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>642124</t>
+          <t>639499</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>719467</t>
+          <t>718132</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1298427</t>
+          <t>1298559</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1410523</t>
+          <t>1409638</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,65%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>36695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64618</t>
+          <t>64200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51616</t>
+          <t>51190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83684</t>
+          <t>82969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88175</t>
+          <t>89815</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125989</t>
+          <t>128049</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34184</t>
+          <t>34996</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>61941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131956</t>
+          <t>130592</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>175295</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>218309</t>
+          <t>217935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>265373</t>
+          <t>266685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203162</t>
+          <t>199958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>245756</t>
+          <t>244695</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>433305</t>
+          <t>432625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>497464</t>
+          <t>495808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128540</t>
+          <t>126197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173276</t>
+          <t>169560</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158789</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199821</t>
+          <t>203958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296905</t>
+          <t>297206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359422</t>
+          <t>357533</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>125444</t>
+          <t>124620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>171384</t>
+          <t>171386</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40857</t>
+          <t>41070</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71785</t>
+          <t>69535</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>176021</t>
+          <t>180170</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>231578</t>
+          <t>234344</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>362478</t>
+          <t>359237</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>439353</t>
+          <t>434740</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>166127</t>
+          <t>165323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>216311</t>
+          <t>220830</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>543886</t>
+          <t>541566</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>635218</t>
+          <t>636365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1304939</t>
+          <t>1307327</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1416437</t>
+          <t>1418022</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1481928</t>
+          <t>1481288</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1601755</t>
+          <t>1597037</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2813236</t>
+          <t>2815983</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2974585</t>
+          <t>2976315</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1269057</t>
+          <t>1266243</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1384498</t>
+          <t>1378935</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1475908</t>
+          <t>1472231</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1591174</t>
+          <t>1591192</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2775725</t>
+          <t>2778487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2940722</t>
+          <t>2944256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14968</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>37575</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>21147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50529</t>
+          <t>50535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39371</t>
+          <t>40293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68503</t>
+          <t>68978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>30650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55988</t>
+          <t>55286</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78332</t>
+          <t>78930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116297</t>
+          <t>116285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>615854</t>
+          <t>614485</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>676055</t>
+          <t>673850</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755049</t>
+          <t>759236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>830818</t>
+          <t>834196</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1394042</t>
+          <t>1388207</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1490344</t>
+          <t>1488282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,42%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>223727</t>
+          <t>223853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>277762</t>
+          <t>279434</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>450354</t>
+          <t>452419</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>523911</t>
+          <t>524013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>689702</t>
+          <t>688118</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>784902</t>
+          <t>780820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>181288</t>
+          <t>178113</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>236941</t>
+          <t>235074</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24981</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49575</t>
+          <t>50627</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>209781</t>
+          <t>213886</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>273346</t>
+          <t>273594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>369510</t>
+          <t>368277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>441973</t>
+          <t>440782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106995</t>
+          <t>106912</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152617</t>
+          <t>153432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>491024</t>
+          <t>488604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>578153</t>
+          <t>580218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>857227</t>
+          <t>851988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>949367</t>
+          <t>948002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1019277</t>
+          <t>1017803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1105477</t>
+          <t>1102449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1897044</t>
+          <t>1899524</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2029795</t>
+          <t>2028680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>410198</t>
+          <t>411600</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>489969</t>
+          <t>491841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>493071</t>
+          <t>492753</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>571957</t>
+          <t>571204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>923247</t>
+          <t>919325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1033916</t>
+          <t>1033926</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42618</t>
+          <t>42186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71389</t>
+          <t>70034</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35770</t>
+          <t>35943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61266</t>
+          <t>62068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95589</t>
+          <t>96738</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120235</t>
+          <t>121426</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>161626</t>
+          <t>166502</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46038</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78031</t>
+          <t>78609</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176574</t>
+          <t>173633</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>231165</t>
+          <t>229717</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>193637</t>
+          <t>195144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241179</t>
+          <t>240568</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>270505</t>
+          <t>268761</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>313887</t>
+          <t>314509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>478102</t>
+          <t>477203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>545016</t>
+          <t>539597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50836</t>
+          <t>48997</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82627</t>
+          <t>82778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67113</t>
+          <t>65882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101668</t>
+          <t>101483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126848</t>
+          <t>127682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174284</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>254113</t>
+          <t>252862</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>321401</t>
+          <t>323071</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53211</t>
+          <t>52565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89101</t>
+          <t>89139</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>322147</t>
+          <t>320153</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>398225</t>
+          <t>398262</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>551385</t>
+          <t>554333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>647065</t>
+          <t>643355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>205093</t>
+          <t>203062</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265099</t>
+          <t>265511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>778225</t>
+          <t>775422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>886536</t>
+          <t>889008</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1706904</t>
+          <t>1710414</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1825072</t>
+          <t>1828793</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2092002</t>
+          <t>2098016</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2209766</t>
+          <t>2219525</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3834415</t>
+          <t>3831802</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4001015</t>
+          <t>4005973</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,46%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>721725</t>
+          <t>717709</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>821006</t>
+          <t>822073</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1042616</t>
+          <t>1038610</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1154525</t>
+          <t>1153094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1793730</t>
+          <t>1788887</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1944759</t>
+          <t>1945040</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>27198</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>14897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35028</t>
+          <t>33057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43126</t>
+          <t>43149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72748</t>
+          <t>71587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24532</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49329</t>
+          <t>48833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73189</t>
+          <t>74048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111025</t>
+          <t>112695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>299690</t>
+          <t>298372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>353863</t>
+          <t>350817</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>363003</t>
+          <t>362622</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>428735</t>
+          <t>427403</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>678188</t>
+          <t>676867</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>755920</t>
+          <t>761178</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>328363</t>
+          <t>329121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>381874</t>
+          <t>382155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>528798</t>
+          <t>527084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>593866</t>
+          <t>590628</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>878087</t>
+          <t>872266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>958231</t>
+          <t>958412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141490</t>
+          <t>141745</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>191385</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35978</t>
+          <t>35954</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64209</t>
+          <t>62963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>186477</t>
+          <t>184537</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>245483</t>
+          <t>241245</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>348697</t>
+          <t>348509</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>419532</t>
+          <t>420756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>184078</t>
+          <t>183944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>241315</t>
+          <t>240621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>551668</t>
+          <t>547377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>639833</t>
+          <t>638548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>817009</t>
+          <t>821435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>911890</t>
+          <t>910566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>889971</t>
+          <t>892603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>983723</t>
+          <t>981784</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1736866</t>
+          <t>1734948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1863251</t>
+          <t>1861883</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>618059</t>
+          <t>617330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>708822</t>
+          <t>708852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>746579</t>
+          <t>751320</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>835102</t>
+          <t>838021</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1395403</t>
+          <t>1391805</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1515975</t>
+          <t>1517228</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46021</t>
+          <t>46489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75794</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32193</t>
+          <t>31346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64533</t>
+          <t>64013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98880</t>
+          <t>99736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>122639</t>
+          <t>125017</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>165263</t>
+          <t>167219</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78021</t>
+          <t>78552</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>113393</t>
+          <t>114471</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>214876</t>
+          <t>216191</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>273162</t>
+          <t>269876</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>194494</t>
+          <t>195433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242481</t>
+          <t>240013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>252269</t>
+          <t>254140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>298288</t>
+          <t>300234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>454131</t>
+          <t>457037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>525334</t>
+          <t>526299</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105643</t>
+          <t>106215</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147545</t>
+          <t>145295</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136504</t>
+          <t>135320</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177786</t>
+          <t>178153</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254448</t>
+          <t>250591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>312730</t>
+          <t>313396</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>211171</t>
+          <t>213120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>272505</t>
+          <t>273598</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58751</t>
+          <t>60583</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93138</t>
+          <t>96474</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>284681</t>
+          <t>283987</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>356260</t>
+          <t>350413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>540751</t>
+          <t>534633</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>633183</t>
+          <t>628620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>307402</t>
+          <t>307774</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>378998</t>
+          <t>382885</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>865175</t>
+          <t>868128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>979635</t>
+          <t>989892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1350473</t>
+          <t>1348845</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1471597</t>
+          <t>1467794</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1547274</t>
+          <t>1544197</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1669519</t>
+          <t>1668149</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2933607</t>
+          <t>2934049</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3093897</t>
+          <t>3098527</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1089899</t>
+          <t>1088595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1200840</t>
+          <t>1197600</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1445027</t>
+          <t>1454193</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1565189</t>
+          <t>1572667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2570666</t>
+          <t>2574073</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2729724</t>
+          <t>2739930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>16709</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22987</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,22 +8284,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>20512</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27308</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33951</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25977</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44099</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30908</t>
+          <t>44321</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18579</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32873</t>
+          <t>40611</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24453</t>
+          <t>29390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45890</t>
+          <t>58576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>213899</t>
+          <t>234012</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>194116</t>
+          <t>212451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>234244</t>
+          <t>255301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>263009</t>
+          <t>288361</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>242186</t>
+          <t>267375</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>282392</t>
+          <t>307761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>476907</t>
+          <t>522373</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>449593</t>
+          <t>491821</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>505303</t>
+          <t>553678</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>262206</t>
+          <t>297056</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>242348</t>
+          <t>275608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>283405</t>
+          <t>319875</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>455086</t>
+          <t>493839</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>434511</t>
+          <t>474250</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>476273</t>
+          <t>515894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>717292</t>
+          <t>790895</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>686643</t>
+          <t>762561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>746146</t>
+          <t>821392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>511431</t>
+          <t>574503</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>511431</t>
+          <t>574503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511431</t>
+          <t>574503</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>749593</t>
+          <t>816596</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>749593</t>
+          <t>816596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>749593</t>
+          <t>816596</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1261024</t>
+          <t>1391099</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1261024</t>
+          <t>1391099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1261024</t>
+          <t>1391099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>269786</t>
+          <t>279733</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>189868</t>
+          <t>244356</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>323994</t>
+          <t>321065</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>131124</t>
+          <t>147846</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92890</t>
+          <t>123777</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>158561</t>
+          <t>170951</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>400910</t>
+          <t>427579</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>319871</t>
+          <t>383322</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>467022</t>
+          <t>477953</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>289444</t>
+          <t>304992</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195912</t>
+          <t>267795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>343592</t>
+          <t>348058</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>120287</t>
+          <t>129837</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83944</t>
+          <t>107757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145634</t>
+          <t>151052</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>409731</t>
+          <t>434830</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>332184</t>
+          <t>389941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>475526</t>
+          <t>484820</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1078408</t>
+          <t>933168</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>918299</t>
+          <t>879607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1462241</t>
+          <t>983468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1227975</t>
+          <t>1075408</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1090279</t>
+          <t>1026231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1501318</t>
+          <t>1114720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2306382</t>
+          <t>2008576</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2045999</t>
+          <t>1940743</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2741059</t>
+          <t>2082664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>647976</t>
+          <t>707859</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>453954</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>744729</t>
+          <t>766270</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>756204</t>
+          <t>815303</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>561571</t>
+          <t>772764</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>866077</t>
+          <t>860698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1404179</t>
+          <t>1523162</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1126116</t>
+          <t>1454160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1592285</t>
+          <t>1587229</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2285614</t>
+          <t>2225753</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2285614</t>
+          <t>2225753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2285614</t>
+          <t>2225753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2235589</t>
+          <t>2168394</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2235589</t>
+          <t>2168394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2235589</t>
+          <t>2168394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4521202</t>
+          <t>4394147</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4521202</t>
+          <t>4394147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4521202</t>
+          <t>4394147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,27 +9387,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>116891</t>
+          <t>131473</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98802</t>
+          <t>108648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140848</t>
+          <t>155022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>87988</t>
+          <t>92377</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73818</t>
+          <t>76762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103880</t>
+          <t>108885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>204879</t>
+          <t>223850</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178252</t>
+          <t>194864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>233604</t>
+          <t>252916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>103585</t>
+          <t>114194</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85325</t>
+          <t>93521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126920</t>
+          <t>138076</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84401</t>
+          <t>89895</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67947</t>
+          <t>72222</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101456</t>
+          <t>107086</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>187986</t>
+          <t>204089</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>163686</t>
+          <t>176752</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>214221</t>
+          <t>234550</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>273903</t>
+          <t>298129</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>242996</t>
+          <t>267797</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>299354</t>
+          <t>327868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>315042</t>
+          <t>355821</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290497</t>
+          <t>331526</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>337118</t>
+          <t>380214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>588945</t>
+          <t>653951</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>554278</t>
+          <t>616663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>625917</t>
+          <t>690919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -9726,27 +9726,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>151195</t>
+          <t>166663</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128283</t>
+          <t>143344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175882</t>
+          <t>193520</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>172655</t>
+          <t>196396</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155106</t>
+          <t>176775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194929</t>
+          <t>219275</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>323851</t>
+          <t>363059</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>295167</t>
+          <t>332513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356072</t>
+          <t>395650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660086</t>
+          <t>734489</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660086</t>
+          <t>734489</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660086</t>
+          <t>734489</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1305660</t>
+          <t>1444948</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1305660</t>
+          <t>1444948</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1305660</t>
+          <t>1444948</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>401516</t>
+          <t>427915</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>310490</t>
+          <t>385845</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>457938</t>
+          <t>479838</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>238224</t>
+          <t>260734</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>193540</t>
+          <t>229611</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>272549</t>
+          <t>291416</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>639739</t>
+          <t>688649</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>547303</t>
+          <t>633765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>712621</t>
+          <t>747954</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>413516</t>
+          <t>445913</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>328541</t>
+          <t>394746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>473320</t>
+          <t>496382</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>217074</t>
+          <t>233617</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179392</t>
+          <t>204335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251548</t>
+          <t>264511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>630590</t>
+          <t>679530</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539644</t>
+          <t>624235</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>704728</t>
+          <t>741682</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1566209</t>
+          <t>1465309</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1402939</t>
+          <t>1397507</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2020579</t>
+          <t>1533140</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1806025</t>
+          <t>1719590</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1656519</t>
+          <t>1664361</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2124193</t>
+          <t>1775413</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3372234</t>
+          <t>3184900</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3113867</t>
+          <t>3102932</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3932013</t>
+          <t>3270505</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1061378</t>
+          <t>1171578</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>823313</t>
+          <t>1114665</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1170032</t>
+          <t>1238218</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1383945</t>
+          <t>1505538</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1163248</t>
+          <t>1454104</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1509427</t>
+          <t>1562423</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2445323</t>
+          <t>2677115</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2087516</t>
+          <t>2601492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2627564</t>
+          <t>2759777</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3442618</t>
+          <t>3510715</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3442618</t>
+          <t>3510715</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3442618</t>
+          <t>3510715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3645268</t>
+          <t>3719479</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3645268</t>
+          <t>3719479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3645268</t>
+          <t>3719479</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7087886</t>
+          <t>7230194</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7087886</t>
+          <t>7230194</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7087886</t>
+          <t>7230194</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
